--- a/reports/pdf_change_20261012.xlsx
+++ b/reports/pdf_change_20261012.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,326억   ·   현금 12억(0.2%)      당일 2026-10-12  vs  전영업일 2026-10-08      매수 4종목  /  매도 7종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,364억      당일 2026-10-12  vs  전영업일 2026-10-08      매수 4종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>71</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1145758646</v>
+        <v>1144590696</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-35</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-499917468</v>
+        <v>-499407868</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>31</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>2673126192</v>
+        <v>2670401292</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-17</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1549292889</v>
+        <v>-1547713589</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>496385868</v>
+        <v>495879868</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-16</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-412804691</v>
+        <v>-412383891</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>509433165</v>
+        <v>508913865</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-423203288</v>
+        <v>-862007771</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.50%</t>
+          <t>0.31%→0.12%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>88→76</t>
+          <t>21→9</t>
         </is>
       </c>
     </row>
@@ -844,23 +844,23 @@
       <c r="E10" s="17" t="n"/>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-862887371</v>
+        <v>-422771888</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.31%→0.12%</t>
+          <t>0.58%→0.50%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>21→9</t>
+          <t>88→76</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
         <v>-6</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-298420121</v>
+        <v>-298115921</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>-3</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-915272757</v>
+        <v>-914339757</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
     <row r="14" ht="19" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,467억   ·   현금 27억(0.8%)      당일 2026-10-12  vs  전영업일 2026-10-08      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,314억      당일 2026-10-12  vs  전영업일 2026-10-08      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B14" s="4" t="n"/>
@@ -947,7 +947,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,834억   ·   현금 34억(1.2%)      당일 2026-10-12  vs  전영업일 2026-10-08      매수 6종목  /  매도 9종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,827억      당일 2026-10-12  vs  전영업일 2026-10-08      매수 6종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -1043,7 +1043,7 @@
         <v>31</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1331729441</v>
+        <v>1325721601</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>-96</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1784328590</v>
+        <v>-1776278937</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1080,23 +1080,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2786350922</v>
+        <v>802344242</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2.91%→3.97%</t>
+          <t>3.20%→3.59%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>60→80</t>
+          <t>230→250</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1108,7 +1108,7 @@
         <v>-66</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1248670913</v>
+        <v>-1243037776</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1124,111 +1124,111 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>805980267</v>
+        <v>2773780838</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>3.20%→3.59%</t>
+          <t>2.91%→3.97%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>230→250</t>
+          <t>60→80</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-874475289</v>
+        <v>-925145279</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.54%→0.19%</t>
+          <t>0.33%→0.00%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>80→30</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>916702803</v>
+        <v>1244229376</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>2.82%→3.14%</t>
+          <t>1.95%→2.67%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>129→144</t>
+          <t>75→90</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (편출)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-929337807</v>
+        <v>-870530263</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.00%</t>
+          <t>0.54%→0.19%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>80→30</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>1249867913</v>
+        <v>912567276</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>1.95%→2.67%</t>
+          <t>2.82%→3.14%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>75→90</t>
+          <t>129→144</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -1240,7 +1240,7 @@
         <v>-33</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1193808395</v>
+        <v>-1188422759</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>4529981499</v>
+        <v>4509545362</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>-30</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-1366575452</v>
+        <v>-1360410411</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>-28</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-660079218</v>
+        <v>-657101399</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>-17</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-2724505901</v>
+        <v>-2712214819</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>-10</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-456190151</v>
+        <v>-454132137</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,225억   ·   현금 9억(0.4%)      당일 2026-10-12  vs  전영업일 2026-10-08      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,114억      당일 2026-10-12  vs  전영업일 2026-10-08      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 315억   ·   현금 4억(1.1%)      당일 2026-10-12  vs  전영업일 2026-10-08      매수 3종목  /  매도 5종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 321억      당일 2026-10-12  vs  전영업일 2026-10-08      매수 3종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1504,11 +1504,11 @@
         <v>42</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>14237156</v>
+        <v>13894444</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>2.79%→2.84%</t>
+          <t>2.67%→2.72%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
@@ -1525,11 +1525,11 @@
         <v>-32</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-25850872</v>
+        <v>-25937928</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>1.53%→1.45%</t>
+          <t>1.50%→1.42%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
@@ -1541,23 +1541,23 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>46647986</v>
+        <v>81940024</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>2.57%→2.73%</t>
+          <t>0.98%→1.24%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>86→91</t>
+          <t>19→24</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
@@ -1569,11 +1569,11 @@
         <v>-21</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-35057390</v>
+        <v>-36414011</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>2.68%→2.57%</t>
+          <t>2.73%→2.62%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -1585,23 +1585,23 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>87379974</v>
+        <v>49334015</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>1.06%→1.35%</t>
+          <t>2.67%→2.83%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>19→24</t>
+          <t>86→91</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -1613,11 +1613,11 @@
         <v>-12</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-39779988</v>
+        <v>-46756814</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>1.08%→0.96%</t>
+          <t>1.25%→1.10%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
@@ -1634,23 +1634,23 @@
       <c r="E39" s="17" t="n"/>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-69359980</v>
+        <v>-42602013</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>3.29%→3.07%</t>
+          <t>2.41%→2.28%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>74→69</t>
+          <t>90→85</t>
         </is>
       </c>
     </row>
@@ -1662,23 +1662,23 @@
       <c r="E40" s="17" t="n"/>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-37093989</v>
+        <v>-71230021</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>2.14%→2.03%</t>
+          <t>3.31%→3.09%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>90→85</t>
+          <t>74→69</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20261012.xlsx
+++ b/reports/pdf_change_20261012.xlsx
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-862007771</v>
+        <v>-422771888</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.31%→0.12%</t>
+          <t>0.58%→0.50%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>21→9</t>
+          <t>88→76</t>
         </is>
       </c>
     </row>
@@ -844,23 +844,23 @@
       <c r="E10" s="17" t="n"/>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-422771888</v>
+        <v>-862007771</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.50%</t>
+          <t>0.31%→0.12%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>88→76</t>
+          <t>21→9</t>
         </is>
       </c>
     </row>
@@ -1145,23 +1145,23 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (편출)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-925145279</v>
+        <v>-870530263</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.00%</t>
+          <t>0.54%→0.19%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>80→30</t>
         </is>
       </c>
     </row>
@@ -1189,23 +1189,23 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-870530263</v>
+        <v>-925145279</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.54%→0.19%</t>
+          <t>0.33%→0.00%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>80→30</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20261012.xlsx
+++ b/reports/pdf_change_20261012.xlsx
@@ -1145,90 +1145,90 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-870530263</v>
+        <v>-925145279</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.54%→0.19%</t>
+          <t>0.33%→0.00%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>80→30</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1244229376</v>
+        <v>912567276</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>1.95%→2.67%</t>
+          <t>2.82%→3.14%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>75→90</t>
+          <t>129→144</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (편출)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-925145279</v>
+        <v>-870530263</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.00%</t>
+          <t>0.54%→0.19%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>80→30</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>912567276</v>
+        <v>1244229376</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>2.82%→3.14%</t>
+          <t>1.95%→2.67%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>129→144</t>
+          <t>75→90</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -1541,23 +1541,23 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>81940024</v>
+        <v>49334015</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>0.98%→1.24%</t>
+          <t>2.67%→2.83%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>19→24</t>
+          <t>86→91</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
@@ -1585,23 +1585,23 @@
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>49334015</v>
+        <v>81940024</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.83%</t>
+          <t>0.98%→1.24%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>86→91</t>
+          <t>19→24</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">

--- a/reports/pdf_change_20261012.xlsx
+++ b/reports/pdf_change_20261012.xlsx
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>코나아이</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-422771888</v>
+        <v>-862007771</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.50%</t>
+          <t>0.31%→0.12%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>88→76</t>
+          <t>21→9</t>
         </is>
       </c>
     </row>
@@ -844,23 +844,23 @@
       <c r="E10" s="17" t="n"/>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>코나아이</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-862007771</v>
+        <v>-422771888</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.31%→0.12%</t>
+          <t>0.58%→0.50%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>21→9</t>
+          <t>88→76</t>
         </is>
       </c>
     </row>
@@ -1080,23 +1080,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>802344242</v>
+        <v>2773780838</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>3.20%→3.59%</t>
+          <t>2.91%→3.97%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>230→250</t>
+          <t>60→80</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1124,111 +1124,111 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>2773780838</v>
+        <v>802344242</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>2.91%→3.97%</t>
+          <t>3.20%→3.59%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>60→80</t>
+          <t>230→250</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (편출)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-925145279</v>
+        <v>-870530263</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.33%→0.00%</t>
+          <t>0.54%→0.19%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>80→30</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>912567276</v>
+        <v>1244229376</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>2.82%→3.14%</t>
+          <t>1.95%→2.67%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>129→144</t>
+          <t>75→90</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-870530263</v>
+        <v>-925145279</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.54%→0.19%</t>
+          <t>0.33%→0.00%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>80→30</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>1244229376</v>
+        <v>912567276</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>1.95%→2.67%</t>
+          <t>2.82%→3.14%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>75→90</t>
+          <t>129→144</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
